--- a/results/tables/model_comparison.xlsx
+++ b/results/tables/model_comparison.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.22763061523438</v>
+        <v>30.4609432220459</v>
       </c>
       <c r="C2" t="n">
-        <v>35.33197402738595</v>
+        <v>40.56699585061421</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9946051836013794</v>
+        <v>0.9927515983581543</v>
       </c>
       <c r="E2" t="n">
-        <v>20.92566586152095</v>
+        <v>27.6565137593558</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>121.098388671875</v>
+        <v>89.06491088867188</v>
       </c>
       <c r="C3" t="n">
-        <v>208.5150155714211</v>
+        <v>146.7226270786991</v>
       </c>
       <c r="D3" t="n">
-        <v>0.834057629108429</v>
+        <v>0.9230362772941589</v>
       </c>
       <c r="E3" t="n">
-        <v>59.52683585233491</v>
+        <v>24.27082643840675</v>
       </c>
     </row>
   </sheetData>
